--- a/导入资料/下载 (3).xlsx
+++ b/导入资料/下载 (3).xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="26025" windowHeight="12855"/>
   </bookViews>
   <sheets>
     <sheet name="基本信息" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="53">
   <si>
     <t>环境γ辐射剂量率测量记录表</t>
   </si>
@@ -83,6 +83,9 @@
   </si>
   <si>
     <t>响应值Xc（Gy/h）</t>
+  </si>
+  <si>
+    <t>齿之康</t>
   </si>
   <si>
     <t/>
@@ -191,11 +194,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.0_ "/>
   </numFmts>
   <fonts count="30">
     <font>
@@ -425,7 +429,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="40">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -454,6 +458,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -830,7 +840,7 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -854,16 +864,16 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -872,89 +882,89 @@
     <xf numFmtId="0" fontId="24" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -983,16 +993,28 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1356,7 +1378,7 @@
       </c>
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:9">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="16" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1366,11 +1388,11 @@
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" spans="1:9">
-      <c r="A5" s="14" t="s">
+      <c r="A5" s="17" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="6">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -1380,11 +1402,11 @@
       <c r="H5" s="8"/>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:9">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="17" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="6">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -1394,11 +1416,11 @@
       <c r="H6" s="8"/>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:9">
-      <c r="A7" s="14" t="s">
+      <c r="A7" s="17" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="6">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -1408,11 +1430,11 @@
       <c r="H7" s="8"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:9">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="17" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="6">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1422,11 +1444,11 @@
       <c r="H8" s="8"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:9">
-      <c r="A9" s="14" t="s">
+      <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
       <c r="B9" s="6">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1439,11 +1461,11 @@
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:9">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="17" t="s">
         <v>8</v>
       </c>
       <c r="B10" s="6">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1453,11 +1475,11 @@
       <c r="H10" s="8"/>
     </row>
     <row r="11" ht="22" customHeight="1" spans="1:9">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="17" t="s">
         <v>9</v>
       </c>
       <c r="B11" s="6">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1467,11 +1489,11 @@
       <c r="H11" s="8"/>
     </row>
     <row r="12" ht="22" customHeight="1" spans="1:9">
-      <c r="A12" s="14" t="s">
+      <c r="A12" s="17" t="s">
         <v>10</v>
       </c>
       <c r="B12" s="6">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1481,27 +1503,27 @@
       <c r="H12" s="8"/>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:9">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="18" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" spans="1:9">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="16" t="s">
+      <c r="C15" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="19" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1509,280 +1531,220 @@
       <c r="A16" s="5">
         <v>1</v>
       </c>
-      <c r="B16" s="5">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5">
-        <v>1</v>
-      </c>
-      <c r="D16" s="5">
-        <v>1</v>
-      </c>
-      <c r="E16" s="5">
-        <v>1</v>
+      <c r="B16" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C16" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D16" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E16" s="12">
+        <v>385</v>
       </c>
       <c r="F16" s="5">
-        <v>1</v>
+        <v>9.692907452</v>
       </c>
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:6">
       <c r="A17" s="5">
         <v>2</v>
       </c>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5">
-        <v>1</v>
-      </c>
-      <c r="D17" s="5">
-        <v>1</v>
-      </c>
-      <c r="E17" s="5">
-        <v>1</v>
+      <c r="B17" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C17" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D17" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E17" s="12">
+        <v>385</v>
       </c>
       <c r="F17" s="5">
-        <v>1</v>
+        <v>9.692907452</v>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1" spans="1:6">
       <c r="A18" s="5">
         <v>3</v>
       </c>
-      <c r="B18" s="5">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5">
-        <v>1</v>
-      </c>
-      <c r="D18" s="5">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5">
-        <v>1</v>
+      <c r="B18" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D18" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E18" s="12">
+        <v>385</v>
       </c>
       <c r="F18" s="5">
-        <v>1</v>
+        <v>9.692907452</v>
       </c>
     </row>
     <row r="19" ht="20" customHeight="1" spans="1:6">
       <c r="A19" s="5">
         <v>4</v>
       </c>
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5">
-        <v>1</v>
-      </c>
-      <c r="D19" s="5">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5">
-        <v>1</v>
+      <c r="B19" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C19" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D19" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E19" s="12">
+        <v>385</v>
       </c>
       <c r="F19" s="5">
-        <v>1</v>
+        <v>9.692907452</v>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1" spans="1:6">
       <c r="A20" s="5">
         <v>5</v>
       </c>
-      <c r="B20" s="5">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5">
-        <v>1</v>
-      </c>
-      <c r="D20" s="5">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5">
-        <v>1</v>
+      <c r="B20" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C20" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D20" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E20" s="12">
+        <v>385</v>
       </c>
       <c r="F20" s="5">
-        <v>1</v>
+        <v>9.692907452</v>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1" spans="1:6">
       <c r="A21" s="5">
         <v>6</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5">
-        <v>1</v>
-      </c>
-      <c r="D21" s="5">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5">
-        <v>1</v>
+      <c r="B21" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C21" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D21" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E21" s="12">
+        <v>385</v>
       </c>
       <c r="F21" s="5">
-        <v>1</v>
+        <v>9.692907452</v>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1" spans="1:6">
       <c r="A22" s="5">
         <v>7</v>
       </c>
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5">
-        <v>1</v>
-      </c>
-      <c r="D22" s="5">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5">
-        <v>1</v>
+      <c r="B22" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="C22" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D22" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E22" s="12">
+        <v>385</v>
       </c>
       <c r="F22" s="5">
-        <v>1</v>
+        <v>9.692907452</v>
       </c>
     </row>
     <row r="23" ht="20" customHeight="1" spans="1:6">
       <c r="A23" s="5">
         <v>8</v>
       </c>
-      <c r="B23" s="5">
-        <v>1</v>
-      </c>
-      <c r="C23" s="5">
-        <v>1</v>
-      </c>
-      <c r="D23" s="5">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5">
-        <v>1</v>
-      </c>
-      <c r="F23" s="5">
-        <v>1</v>
-      </c>
+      <c r="B23" s="5"/>
+      <c r="C23" s="5"/>
+      <c r="D23" s="5"/>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:6">
       <c r="A24" s="5">
         <v>9</v>
       </c>
-      <c r="B24" s="5">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5">
-        <v>1</v>
-      </c>
-      <c r="D24" s="5">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5">
-        <v>1</v>
-      </c>
-      <c r="F24" s="5">
-        <v>1</v>
-      </c>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
+      <c r="D24" s="5"/>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
     </row>
     <row r="25" ht="20" customHeight="1" spans="1:6">
       <c r="A25" s="5">
         <v>10</v>
       </c>
-      <c r="B25" s="5">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5">
-        <v>1</v>
-      </c>
-      <c r="D25" s="5">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5">
-        <v>1</v>
-      </c>
-      <c r="F25" s="5">
-        <v>1</v>
-      </c>
+      <c r="B25" s="5"/>
+      <c r="C25" s="5"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6">
       <c r="A26" s="5">
         <v>11</v>
       </c>
-      <c r="B26" s="5">
-        <v>1</v>
-      </c>
-      <c r="C26" s="5">
-        <v>1</v>
-      </c>
-      <c r="D26" s="5">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5">
-        <v>1</v>
-      </c>
-      <c r="F26" s="5">
-        <v>1</v>
-      </c>
+      <c r="B26" s="5"/>
+      <c r="C26" s="5"/>
+      <c r="D26" s="5"/>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6">
       <c r="A27" s="5">
         <v>12</v>
       </c>
-      <c r="B27" s="5">
-        <v>1</v>
-      </c>
-      <c r="C27" s="5">
-        <v>1</v>
-      </c>
-      <c r="D27" s="5">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5">
-        <v>1</v>
-      </c>
-      <c r="F27" s="5">
-        <v>1</v>
-      </c>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="5"/>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
     </row>
     <row r="28" ht="20" customHeight="1" spans="1:6">
       <c r="A28" s="5">
         <v>13</v>
       </c>
-      <c r="B28" s="5">
-        <v>1</v>
-      </c>
-      <c r="C28" s="5">
-        <v>1</v>
-      </c>
-      <c r="D28" s="5">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5">
-        <v>1</v>
-      </c>
-      <c r="F28" s="5">
-        <v>1</v>
-      </c>
+      <c r="B28" s="5"/>
+      <c r="C28" s="5"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
     </row>
     <row r="29" ht="20" customHeight="1" spans="1:6">
       <c r="A29" s="5">
         <v>14</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="30" ht="20" customHeight="1" spans="1:6">
@@ -1790,19 +1752,19 @@
         <v>15</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31" ht="20" customHeight="1" spans="1:6">
@@ -1810,19 +1772,19 @@
         <v>16</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32" ht="20" customHeight="1" spans="1:6">
@@ -1830,19 +1792,19 @@
         <v>17</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33" ht="20" customHeight="1" spans="1:6">
@@ -1850,19 +1812,19 @@
         <v>18</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1" spans="1:6">
@@ -1870,19 +1832,19 @@
         <v>19</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" ht="20" customHeight="1" spans="1:6">
@@ -1890,19 +1852,19 @@
         <v>20</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36" ht="20" customHeight="1" spans="1:6">
@@ -1910,19 +1872,19 @@
         <v>21</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" ht="20" customHeight="1" spans="1:6">
@@ -1930,19 +1892,19 @@
         <v>22</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:6">
@@ -1950,19 +1912,19 @@
         <v>23</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:6">
@@ -1970,19 +1932,19 @@
         <v>24</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1" spans="1:6">
@@ -1990,19 +1952,19 @@
         <v>25</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41" ht="20" customHeight="1" spans="1:6">
@@ -2010,19 +1972,19 @@
         <v>26</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" ht="20" customHeight="1" spans="1:6">
@@ -2030,19 +1992,19 @@
         <v>27</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="43" ht="20" customHeight="1" spans="1:6">
@@ -2050,19 +2012,19 @@
         <v>28</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="44" ht="20" customHeight="1" spans="1:6">
@@ -2070,19 +2032,19 @@
         <v>29</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="45" ht="20" customHeight="1" spans="1:6">
@@ -2090,19 +2052,19 @@
         <v>30</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" ht="20" customHeight="1" spans="1:6">
@@ -2110,19 +2072,19 @@
         <v>31</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="47" ht="20" customHeight="1" spans="1:6">
@@ -2130,19 +2092,19 @@
         <v>32</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" ht="20" customHeight="1" spans="1:6">
@@ -2150,19 +2112,19 @@
         <v>33</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:6">
@@ -2170,19 +2132,19 @@
         <v>34</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:6">
@@ -2190,19 +2152,19 @@
         <v>35</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:6">
@@ -2210,19 +2172,19 @@
         <v>36</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" ht="20" customHeight="1" spans="1:6">
@@ -2230,19 +2192,19 @@
         <v>37</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" ht="20" customHeight="1" spans="1:6">
@@ -2250,19 +2212,19 @@
         <v>38</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" ht="20" customHeight="1" spans="1:6">
@@ -2270,19 +2232,19 @@
         <v>39</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C54" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" ht="20" customHeight="1" spans="1:6">
@@ -2290,19 +2252,19 @@
         <v>40</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C55" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D55" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" ht="20" customHeight="1" spans="1:6">
@@ -2310,19 +2272,19 @@
         <v>41</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C56" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D56" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="57" ht="20" customHeight="1" spans="1:6">
@@ -2330,19 +2292,19 @@
         <v>42</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:6">
@@ -2350,19 +2312,19 @@
         <v>43</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:6">
@@ -2370,19 +2332,19 @@
         <v>44</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="60" ht="20" customHeight="1" spans="1:6">
@@ -2390,19 +2352,19 @@
         <v>45</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:6">
@@ -2410,19 +2372,19 @@
         <v>46</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:6">
@@ -2430,19 +2392,19 @@
         <v>47</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:6">
@@ -2450,19 +2412,19 @@
         <v>48</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C63" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D63" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:6">
@@ -2470,19 +2432,19 @@
         <v>49</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C64" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" ht="20" customHeight="1" spans="1:6">
@@ -2490,44 +2452,44 @@
         <v>50</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C65" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D65" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F65" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="67" ht="22" customHeight="1" spans="1:6">
-      <c r="A67" s="15" t="s">
-        <v>19</v>
+      <c r="A67" s="18" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="68" ht="22" customHeight="1" spans="1:6">
-      <c r="A68" s="16" t="s">
+      <c r="A68" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="B68" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C68" s="16" t="s">
+      <c r="B68" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="D68" s="16" t="s">
+      <c r="C68" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="D68" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E68" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F68" s="16" t="s">
+      <c r="E68" s="19" t="s">
         <v>23</v>
+      </c>
+      <c r="F68" s="19" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="69" ht="20" customHeight="1" spans="1:6">
@@ -2735,19 +2697,19 @@
         <v>11</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="80" ht="20" customHeight="1" spans="1:6">
@@ -2755,19 +2717,19 @@
         <v>12</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81" ht="20" customHeight="1" spans="1:6">
@@ -2775,19 +2737,19 @@
         <v>13</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C81" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D81" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="82" ht="20" customHeight="1" spans="1:6">
@@ -2795,19 +2757,19 @@
         <v>14</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C82" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D82" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F82" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" ht="20" customHeight="1" spans="1:6">
@@ -2815,19 +2777,19 @@
         <v>15</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C83" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D83" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" ht="20" customHeight="1" spans="1:6">
@@ -2835,19 +2797,19 @@
         <v>16</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C84" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D84" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F84" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="85" ht="20" customHeight="1" spans="1:6">
@@ -2855,19 +2817,19 @@
         <v>17</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C85" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D85" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F85" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1" spans="1:6">
@@ -2875,19 +2837,19 @@
         <v>18</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C86" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D86" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F86" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="87" ht="20" customHeight="1" spans="1:6">
@@ -2895,19 +2857,19 @@
         <v>19</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C87" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D87" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1" spans="1:6">
@@ -2915,19 +2877,19 @@
         <v>20</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D88" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F88" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="89" ht="20" customHeight="1" spans="1:6">
@@ -2935,19 +2897,19 @@
         <v>21</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C89" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D89" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1" spans="1:6">
@@ -2955,19 +2917,19 @@
         <v>22</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C90" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D90" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1" spans="1:6">
@@ -2975,19 +2937,19 @@
         <v>23</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="92" ht="20" customHeight="1" spans="1:6">
@@ -2995,19 +2957,19 @@
         <v>24</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C92" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93" ht="20" customHeight="1" spans="1:6">
@@ -3015,19 +2977,19 @@
         <v>25</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C93" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F93" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94" ht="20" customHeight="1" spans="1:6">
@@ -3035,19 +2997,19 @@
         <v>26</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C94" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F94" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="95" ht="20" customHeight="1" spans="1:6">
@@ -3055,19 +3017,19 @@
         <v>27</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C95" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F95" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="96" ht="20" customHeight="1" spans="1:6">
@@ -3075,19 +3037,19 @@
         <v>28</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C96" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F96" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="97" ht="20" customHeight="1" spans="1:6">
@@ -3095,19 +3057,19 @@
         <v>29</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C97" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="98" ht="20" customHeight="1" spans="1:6">
@@ -3115,19 +3077,19 @@
         <v>30</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F98" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="99" ht="20" customHeight="1" spans="1:6">
@@ -3135,19 +3097,19 @@
         <v>31</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C99" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D99" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F99" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100" ht="20" customHeight="1" spans="1:6">
@@ -3155,19 +3117,19 @@
         <v>32</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C100" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D100" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101" ht="20" customHeight="1" spans="1:6">
@@ -3175,19 +3137,19 @@
         <v>33</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C101" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D101" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F101" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="102" ht="20" customHeight="1" spans="1:6">
@@ -3195,19 +3157,19 @@
         <v>34</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C102" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D102" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E102" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F102" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="103" ht="20" customHeight="1" spans="1:6">
@@ -3215,19 +3177,19 @@
         <v>35</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C103" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D103" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E103" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F103" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="104" ht="20" customHeight="1" spans="1:6">
@@ -3235,19 +3197,19 @@
         <v>36</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C104" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D104" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E104" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="105" ht="20" customHeight="1" spans="1:6">
@@ -3255,19 +3217,19 @@
         <v>37</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C105" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D105" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E105" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F105" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="106" ht="20" customHeight="1" spans="1:6">
@@ -3275,19 +3237,19 @@
         <v>38</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C106" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D106" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E106" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="107" ht="20" customHeight="1" spans="1:6">
@@ -3295,19 +3257,19 @@
         <v>39</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C107" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D107" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E107" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F107" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="108" ht="20" customHeight="1" spans="1:6">
@@ -3315,19 +3277,19 @@
         <v>40</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C108" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D108" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E108" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F108" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="109" ht="20" customHeight="1" spans="1:6">
@@ -3335,19 +3297,19 @@
         <v>41</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C109" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D109" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E109" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F109" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="110" ht="20" customHeight="1" spans="1:6">
@@ -3355,19 +3317,19 @@
         <v>42</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C110" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D110" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E110" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="111" ht="20" customHeight="1" spans="1:6">
@@ -3375,19 +3337,19 @@
         <v>43</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C111" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D111" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E111" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="112" ht="20" customHeight="1" spans="1:6">
@@ -3395,19 +3357,19 @@
         <v>44</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C112" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D112" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E112" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="113" ht="20" customHeight="1" spans="1:6">
@@ -3415,19 +3377,19 @@
         <v>45</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C113" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D113" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E113" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="114" ht="20" customHeight="1" spans="1:6">
@@ -3435,19 +3397,19 @@
         <v>46</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C114" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D114" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E114" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F114" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="115" ht="20" customHeight="1" spans="1:6">
@@ -3455,19 +3417,19 @@
         <v>47</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C115" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D115" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E115" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F115" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="116" ht="20" customHeight="1" spans="1:6">
@@ -3475,19 +3437,19 @@
         <v>48</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C116" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D116" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E116" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F116" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117" ht="20" customHeight="1" spans="1:6">
@@ -3495,19 +3457,19 @@
         <v>49</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C117" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D117" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E117" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="118" ht="20" customHeight="1" spans="1:6">
@@ -3515,19 +3477,19 @@
         <v>50</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C118" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D118" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E118" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F118" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -3570,15 +3532,15 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:15">
       <c r="A1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1" spans="1:15">
       <c r="A2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>14</v>
@@ -3590,34 +3552,34 @@
         <v>16</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O2" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" ht="18" customHeight="1" spans="1:15">
@@ -3627,92 +3589,76 @@
       <c r="B3" s="11">
         <v>1</v>
       </c>
-      <c r="C3" s="10">
-        <v>1</v>
-      </c>
-      <c r="D3" s="10">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10">
-        <v>1</v>
-      </c>
-      <c r="F3" s="10">
-        <v>1</v>
-      </c>
-      <c r="G3" s="10">
-        <v>1</v>
-      </c>
-      <c r="H3" s="10">
-        <v>1</v>
-      </c>
-      <c r="I3" s="11">
-        <v>1</v>
-      </c>
-      <c r="J3" s="10">
-        <v>1</v>
-      </c>
-      <c r="K3" s="10">
-        <v>1</v>
-      </c>
-      <c r="L3" s="10">
-        <v>1</v>
-      </c>
-      <c r="M3" s="10">
-        <v>1</v>
-      </c>
-      <c r="N3" s="10">
-        <v>1</v>
-      </c>
-      <c r="O3" s="10">
-        <v>1</v>
-      </c>
+      <c r="C3" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D3" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E3" s="12">
+        <v>385</v>
+      </c>
+      <c r="F3" s="13">
+        <v>125</v>
+      </c>
+      <c r="G3" s="13">
+        <v>123</v>
+      </c>
+      <c r="H3" s="13">
+        <v>124</v>
+      </c>
+      <c r="I3" s="13">
+        <v>125</v>
+      </c>
+      <c r="J3" s="13">
+        <v>126</v>
+      </c>
+      <c r="K3" s="10"/>
+      <c r="L3" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="M3" s="10"/>
+      <c r="N3" s="10"/>
+      <c r="O3" s="10"/>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:15">
-      <c r="A4" s="12">
+      <c r="A4" s="15">
         <v>2</v>
       </c>
       <c r="B4" s="11">
         <v>2</v>
       </c>
-      <c r="C4" s="10">
-        <v>2</v>
-      </c>
-      <c r="D4" s="10">
-        <v>2</v>
-      </c>
-      <c r="E4" s="10">
-        <v>2</v>
-      </c>
-      <c r="F4" s="10">
-        <v>2</v>
-      </c>
-      <c r="G4" s="10">
-        <v>2</v>
-      </c>
-      <c r="H4" s="10">
-        <v>2</v>
-      </c>
-      <c r="I4" s="11">
-        <v>2</v>
-      </c>
-      <c r="J4" s="10">
-        <v>2</v>
-      </c>
-      <c r="K4" s="10">
-        <v>2</v>
-      </c>
-      <c r="L4" s="10">
-        <v>2</v>
-      </c>
-      <c r="M4" s="10">
-        <v>2</v>
-      </c>
-      <c r="N4" s="10">
-        <v>2</v>
-      </c>
-      <c r="O4" s="10">
-        <v>2</v>
-      </c>
+      <c r="C4" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D4" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E4" s="12">
+        <v>385</v>
+      </c>
+      <c r="F4" s="13">
+        <v>118</v>
+      </c>
+      <c r="G4" s="13">
+        <v>117</v>
+      </c>
+      <c r="H4" s="13">
+        <v>118</v>
+      </c>
+      <c r="I4" s="13">
+        <v>119</v>
+      </c>
+      <c r="J4" s="13">
+        <v>119</v>
+      </c>
+      <c r="K4" s="10"/>
+      <c r="L4" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="M4" s="10"/>
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
     </row>
     <row r="5" ht="18" customHeight="1" spans="1:15">
       <c r="A5" s="10">
@@ -3721,92 +3667,76 @@
       <c r="B5" s="11">
         <v>3</v>
       </c>
-      <c r="C5" s="10">
-        <v>3</v>
-      </c>
-      <c r="D5" s="10">
-        <v>3</v>
-      </c>
-      <c r="E5" s="10">
-        <v>3</v>
-      </c>
-      <c r="F5" s="10">
-        <v>3</v>
-      </c>
-      <c r="G5" s="10">
-        <v>3</v>
-      </c>
-      <c r="H5" s="10">
-        <v>3</v>
-      </c>
-      <c r="I5" s="11">
-        <v>3</v>
-      </c>
-      <c r="J5" s="10">
-        <v>3</v>
-      </c>
-      <c r="K5" s="10">
-        <v>3</v>
-      </c>
-      <c r="L5" s="10">
-        <v>3</v>
-      </c>
-      <c r="M5" s="10">
-        <v>3</v>
-      </c>
-      <c r="N5" s="10">
-        <v>3</v>
-      </c>
-      <c r="O5" s="10">
-        <v>3</v>
-      </c>
+      <c r="C5" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D5" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E5" s="12">
+        <v>385</v>
+      </c>
+      <c r="F5" s="13">
+        <v>119</v>
+      </c>
+      <c r="G5" s="13">
+        <v>118</v>
+      </c>
+      <c r="H5" s="13">
+        <v>116</v>
+      </c>
+      <c r="I5" s="13">
+        <v>117</v>
+      </c>
+      <c r="J5" s="13">
+        <v>119</v>
+      </c>
+      <c r="K5" s="10"/>
+      <c r="L5" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
     </row>
     <row r="6" ht="18" customHeight="1" spans="1:15">
-      <c r="A6" s="12">
+      <c r="A6" s="15">
         <v>4</v>
       </c>
       <c r="B6" s="11">
         <v>4</v>
       </c>
-      <c r="C6" s="10">
-        <v>4</v>
-      </c>
-      <c r="D6" s="10">
-        <v>4</v>
-      </c>
-      <c r="E6" s="10">
-        <v>4</v>
-      </c>
-      <c r="F6" s="10">
-        <v>4</v>
-      </c>
-      <c r="G6" s="10">
-        <v>4</v>
-      </c>
-      <c r="H6" s="10">
-        <v>4</v>
-      </c>
-      <c r="I6" s="11">
-        <v>4</v>
-      </c>
-      <c r="J6" s="10">
-        <v>4</v>
-      </c>
-      <c r="K6" s="10">
-        <v>4</v>
-      </c>
-      <c r="L6" s="10">
-        <v>4</v>
-      </c>
-      <c r="M6" s="10">
-        <v>4</v>
-      </c>
-      <c r="N6" s="10">
-        <v>4</v>
-      </c>
-      <c r="O6" s="10">
-        <v>4</v>
-      </c>
+      <c r="C6" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D6" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E6" s="12">
+        <v>385</v>
+      </c>
+      <c r="F6" s="13">
+        <v>117</v>
+      </c>
+      <c r="G6" s="13">
+        <v>118</v>
+      </c>
+      <c r="H6" s="13">
+        <v>119</v>
+      </c>
+      <c r="I6" s="13">
+        <v>120</v>
+      </c>
+      <c r="J6" s="13">
+        <v>121</v>
+      </c>
+      <c r="K6" s="10"/>
+      <c r="L6" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="M6" s="10"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
     </row>
     <row r="7" ht="18" customHeight="1" spans="1:15">
       <c r="A7" s="10">
@@ -3815,92 +3745,76 @@
       <c r="B7" s="11">
         <v>5</v>
       </c>
-      <c r="C7" s="10">
-        <v>5</v>
-      </c>
-      <c r="D7" s="10">
-        <v>5</v>
-      </c>
-      <c r="E7" s="10">
-        <v>5</v>
-      </c>
-      <c r="F7" s="10">
-        <v>5</v>
-      </c>
-      <c r="G7" s="10">
-        <v>5</v>
-      </c>
-      <c r="H7" s="10">
-        <v>5</v>
-      </c>
-      <c r="I7" s="11">
-        <v>5</v>
-      </c>
-      <c r="J7" s="10">
-        <v>5</v>
-      </c>
-      <c r="K7" s="10">
-        <v>5</v>
-      </c>
-      <c r="L7" s="10">
-        <v>5</v>
-      </c>
-      <c r="M7" s="10">
-        <v>5</v>
-      </c>
-      <c r="N7" s="10">
-        <v>5</v>
-      </c>
-      <c r="O7" s="10">
-        <v>5</v>
-      </c>
+      <c r="C7" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D7" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E7" s="12">
+        <v>385</v>
+      </c>
+      <c r="F7" s="13">
+        <v>123</v>
+      </c>
+      <c r="G7" s="13">
+        <v>120</v>
+      </c>
+      <c r="H7" s="13">
+        <v>119</v>
+      </c>
+      <c r="I7" s="13">
+        <v>120</v>
+      </c>
+      <c r="J7" s="13">
+        <v>121</v>
+      </c>
+      <c r="K7" s="10"/>
+      <c r="L7" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="M7" s="10"/>
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
     </row>
     <row r="8" ht="18" customHeight="1" spans="1:15">
-      <c r="A8" s="12">
+      <c r="A8" s="15">
         <v>6</v>
       </c>
       <c r="B8" s="11">
         <v>6</v>
       </c>
-      <c r="C8" s="10">
-        <v>6</v>
-      </c>
-      <c r="D8" s="10">
-        <v>6</v>
-      </c>
-      <c r="E8" s="10">
-        <v>6</v>
-      </c>
-      <c r="F8" s="10">
-        <v>6</v>
-      </c>
-      <c r="G8" s="10">
-        <v>6</v>
-      </c>
-      <c r="H8" s="10">
-        <v>6</v>
-      </c>
-      <c r="I8" s="11">
-        <v>6</v>
-      </c>
-      <c r="J8" s="10">
-        <v>6</v>
-      </c>
-      <c r="K8" s="10">
-        <v>6</v>
-      </c>
-      <c r="L8" s="10">
-        <v>6</v>
-      </c>
-      <c r="M8" s="10">
-        <v>6</v>
-      </c>
-      <c r="N8" s="10">
-        <v>6</v>
-      </c>
-      <c r="O8" s="10">
-        <v>6</v>
-      </c>
+      <c r="C8" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D8" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E8" s="12">
+        <v>385</v>
+      </c>
+      <c r="F8" s="13">
+        <v>120</v>
+      </c>
+      <c r="G8" s="13">
+        <v>123</v>
+      </c>
+      <c r="H8" s="13">
+        <v>122</v>
+      </c>
+      <c r="I8" s="13">
+        <v>121</v>
+      </c>
+      <c r="J8" s="13">
+        <v>124</v>
+      </c>
+      <c r="K8" s="10"/>
+      <c r="L8" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="10"/>
+      <c r="N8" s="10"/>
+      <c r="O8" s="10"/>
     </row>
     <row r="9" ht="18" customHeight="1" spans="1:15">
       <c r="A9" s="10">
@@ -3909,844 +3823,360 @@
       <c r="B9" s="11">
         <v>7</v>
       </c>
-      <c r="C9" s="10">
-        <v>7</v>
-      </c>
-      <c r="D9" s="10">
-        <v>7</v>
-      </c>
-      <c r="E9" s="10">
-        <v>7</v>
-      </c>
-      <c r="F9" s="10">
-        <v>7</v>
-      </c>
-      <c r="G9" s="10">
-        <v>7</v>
-      </c>
-      <c r="H9" s="10">
-        <v>7</v>
-      </c>
-      <c r="I9" s="11">
-        <v>7</v>
-      </c>
-      <c r="J9" s="10">
-        <v>7</v>
-      </c>
-      <c r="K9" s="10">
-        <v>7</v>
-      </c>
-      <c r="L9" s="10">
-        <v>7</v>
-      </c>
-      <c r="M9" s="10">
-        <v>7</v>
-      </c>
-      <c r="N9" s="10">
-        <v>7</v>
-      </c>
-      <c r="O9" s="10">
-        <v>7</v>
-      </c>
+      <c r="C9" s="12">
+        <v>108.702694</v>
+      </c>
+      <c r="D9" s="12">
+        <v>34.337444</v>
+      </c>
+      <c r="E9" s="12">
+        <v>385</v>
+      </c>
+      <c r="F9" s="13">
+        <v>83.8</v>
+      </c>
+      <c r="G9" s="13">
+        <v>84</v>
+      </c>
+      <c r="H9" s="13">
+        <v>87</v>
+      </c>
+      <c r="I9" s="13">
+        <v>86.5</v>
+      </c>
+      <c r="J9" s="13">
+        <v>88.7</v>
+      </c>
+      <c r="K9" s="10"/>
+      <c r="L9" s="14">
+        <v>0.8</v>
+      </c>
+      <c r="M9" s="10"/>
+      <c r="N9" s="10"/>
+      <c r="O9" s="10"/>
     </row>
     <row r="10" ht="18" customHeight="1" spans="1:15">
-      <c r="A10" s="12">
+      <c r="A10" s="15">
         <v>8</v>
       </c>
-      <c r="B10" s="11">
-        <v>8</v>
-      </c>
-      <c r="C10" s="10">
-        <v>8</v>
-      </c>
-      <c r="D10" s="10">
-        <v>8</v>
-      </c>
-      <c r="E10" s="10">
-        <v>8</v>
-      </c>
-      <c r="F10" s="10">
-        <v>8</v>
-      </c>
-      <c r="G10" s="10">
-        <v>8</v>
-      </c>
-      <c r="H10" s="10">
-        <v>8</v>
-      </c>
-      <c r="I10" s="11">
-        <v>8</v>
-      </c>
-      <c r="J10" s="10">
-        <v>8</v>
-      </c>
-      <c r="K10" s="10">
-        <v>8</v>
-      </c>
-      <c r="L10" s="10">
-        <v>8</v>
-      </c>
-      <c r="M10" s="10">
-        <v>8</v>
-      </c>
-      <c r="N10" s="10">
-        <v>8</v>
-      </c>
-      <c r="O10" s="10">
-        <v>8</v>
-      </c>
+      <c r="B10" s="11"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="10"/>
+      <c r="I10" s="11"/>
+      <c r="J10" s="10"/>
+      <c r="K10" s="10"/>
+      <c r="L10" s="10"/>
+      <c r="M10" s="10"/>
+      <c r="N10" s="10"/>
+      <c r="O10" s="10"/>
     </row>
     <row r="11" ht="18" customHeight="1" spans="1:15">
       <c r="A11" s="10">
         <v>9</v>
       </c>
-      <c r="B11" s="11">
-        <v>9</v>
-      </c>
-      <c r="C11" s="10">
-        <v>9</v>
-      </c>
-      <c r="D11" s="10">
-        <v>9</v>
-      </c>
-      <c r="E11" s="10">
-        <v>9</v>
-      </c>
-      <c r="F11" s="10">
-        <v>9</v>
-      </c>
-      <c r="G11" s="10">
-        <v>9</v>
-      </c>
-      <c r="H11" s="10">
-        <v>9</v>
-      </c>
-      <c r="I11" s="11">
-        <v>9</v>
-      </c>
-      <c r="J11" s="10">
-        <v>9</v>
-      </c>
-      <c r="K11" s="10">
-        <v>9</v>
-      </c>
-      <c r="L11" s="10">
-        <v>9</v>
-      </c>
-      <c r="M11" s="10">
-        <v>9</v>
-      </c>
-      <c r="N11" s="10">
-        <v>9</v>
-      </c>
-      <c r="O11" s="10">
-        <v>9</v>
-      </c>
+      <c r="B11" s="11"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="10"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="10"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="10"/>
+      <c r="M11" s="10"/>
+      <c r="N11" s="10"/>
+      <c r="O11" s="10"/>
     </row>
     <row r="12" ht="18" customHeight="1" spans="1:15">
-      <c r="A12" s="12">
+      <c r="A12" s="15">
         <v>10</v>
       </c>
-      <c r="B12" s="11">
-        <v>10</v>
-      </c>
-      <c r="C12" s="10">
-        <v>10</v>
-      </c>
-      <c r="D12" s="10">
-        <v>10</v>
-      </c>
-      <c r="E12" s="10">
-        <v>10</v>
-      </c>
-      <c r="F12" s="10">
-        <v>10</v>
-      </c>
-      <c r="G12" s="10">
-        <v>10</v>
-      </c>
-      <c r="H12" s="10">
-        <v>10</v>
-      </c>
-      <c r="I12" s="11">
-        <v>10</v>
-      </c>
-      <c r="J12" s="10">
-        <v>10</v>
-      </c>
-      <c r="K12" s="10">
-        <v>10</v>
-      </c>
-      <c r="L12" s="10">
-        <v>10</v>
-      </c>
-      <c r="M12" s="10">
-        <v>10</v>
-      </c>
-      <c r="N12" s="10">
-        <v>10</v>
-      </c>
-      <c r="O12" s="10">
-        <v>10</v>
-      </c>
+      <c r="B12" s="11"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10"/>
+      <c r="F12" s="10"/>
+      <c r="G12" s="10"/>
+      <c r="H12" s="10"/>
+      <c r="I12" s="11"/>
+      <c r="J12" s="10"/>
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+      <c r="M12" s="10"/>
+      <c r="N12" s="10"/>
+      <c r="O12" s="10"/>
     </row>
     <row r="13" ht="18" customHeight="1" spans="1:15">
       <c r="A13" s="10">
         <v>11</v>
       </c>
-      <c r="B13" s="11">
-        <v>11</v>
-      </c>
-      <c r="C13" s="10">
-        <v>11</v>
-      </c>
-      <c r="D13" s="10">
-        <v>11</v>
-      </c>
-      <c r="E13" s="10">
-        <v>11</v>
-      </c>
-      <c r="F13" s="10">
-        <v>11</v>
-      </c>
-      <c r="G13" s="10">
-        <v>11</v>
-      </c>
-      <c r="H13" s="10">
-        <v>11</v>
-      </c>
-      <c r="I13" s="11">
-        <v>11</v>
-      </c>
-      <c r="J13" s="10">
-        <v>11</v>
-      </c>
-      <c r="K13" s="10">
-        <v>11</v>
-      </c>
-      <c r="L13" s="10">
-        <v>11</v>
-      </c>
-      <c r="M13" s="10">
-        <v>11</v>
-      </c>
-      <c r="N13" s="10">
-        <v>11</v>
-      </c>
-      <c r="O13" s="10">
-        <v>11</v>
-      </c>
+      <c r="B13" s="11"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="11"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+      <c r="M13" s="10"/>
+      <c r="N13" s="10"/>
+      <c r="O13" s="10"/>
     </row>
     <row r="14" ht="18" customHeight="1" spans="1:15">
-      <c r="A14" s="12">
+      <c r="A14" s="15">
         <v>12</v>
       </c>
-      <c r="B14" s="11">
-        <v>12</v>
-      </c>
-      <c r="C14" s="10">
-        <v>12</v>
-      </c>
-      <c r="D14" s="10">
-        <v>12</v>
-      </c>
-      <c r="E14" s="10">
-        <v>12</v>
-      </c>
-      <c r="F14" s="10">
-        <v>12</v>
-      </c>
-      <c r="G14" s="10">
-        <v>12</v>
-      </c>
-      <c r="H14" s="10">
-        <v>12</v>
-      </c>
-      <c r="I14" s="11">
-        <v>12</v>
-      </c>
-      <c r="J14" s="10">
-        <v>12</v>
-      </c>
-      <c r="K14" s="10">
-        <v>12</v>
-      </c>
-      <c r="L14" s="10">
-        <v>12</v>
-      </c>
-      <c r="M14" s="10">
-        <v>12</v>
-      </c>
-      <c r="N14" s="10">
-        <v>12</v>
-      </c>
-      <c r="O14" s="10">
-        <v>12</v>
-      </c>
+      <c r="B14" s="11"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="10"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="11"/>
+      <c r="J14" s="10"/>
+      <c r="K14" s="10"/>
+      <c r="L14" s="10"/>
+      <c r="M14" s="10"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
     </row>
     <row r="15" ht="18" customHeight="1" spans="1:15">
       <c r="A15" s="10">
         <v>13</v>
       </c>
-      <c r="B15" s="11">
-        <v>13</v>
-      </c>
-      <c r="C15" s="10">
-        <v>13</v>
-      </c>
-      <c r="D15" s="10">
-        <v>13</v>
-      </c>
-      <c r="E15" s="10">
-        <v>13</v>
-      </c>
-      <c r="F15" s="10">
-        <v>13</v>
-      </c>
-      <c r="G15" s="10">
-        <v>13</v>
-      </c>
-      <c r="H15" s="10">
-        <v>13</v>
-      </c>
-      <c r="I15" s="11">
-        <v>13</v>
-      </c>
-      <c r="J15" s="10">
-        <v>13</v>
-      </c>
-      <c r="K15" s="10">
-        <v>13</v>
-      </c>
-      <c r="L15" s="10">
-        <v>13</v>
-      </c>
-      <c r="M15" s="10">
-        <v>13</v>
-      </c>
-      <c r="N15" s="10">
-        <v>13</v>
-      </c>
-      <c r="O15" s="10">
-        <v>13</v>
-      </c>
+      <c r="B15" s="11"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="10"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="10"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="10"/>
+      <c r="M15" s="10"/>
+      <c r="N15" s="10"/>
+      <c r="O15" s="10"/>
     </row>
     <row r="16" ht="18" customHeight="1" spans="1:15">
-      <c r="A16" s="12">
+      <c r="A16" s="15">
         <v>14</v>
       </c>
-      <c r="B16" s="11">
-        <v>14</v>
-      </c>
-      <c r="C16" s="10">
-        <v>14</v>
-      </c>
-      <c r="D16" s="10">
-        <v>14</v>
-      </c>
-      <c r="E16" s="10">
-        <v>14</v>
-      </c>
-      <c r="F16" s="10">
-        <v>14</v>
-      </c>
-      <c r="G16" s="10">
-        <v>14</v>
-      </c>
-      <c r="H16" s="10">
-        <v>14</v>
-      </c>
-      <c r="I16" s="11">
-        <v>14</v>
-      </c>
-      <c r="J16" s="10">
-        <v>14</v>
-      </c>
-      <c r="K16" s="10">
-        <v>14</v>
-      </c>
-      <c r="L16" s="10">
-        <v>14</v>
-      </c>
-      <c r="M16" s="10">
-        <v>14</v>
-      </c>
-      <c r="N16" s="10">
-        <v>14</v>
-      </c>
-      <c r="O16" s="10">
-        <v>14</v>
-      </c>
+      <c r="B16" s="11"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="10"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="11"/>
+      <c r="J16" s="10"/>
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+      <c r="M16" s="10"/>
+      <c r="N16" s="10"/>
+      <c r="O16" s="10"/>
     </row>
     <row r="17" ht="18" customHeight="1" spans="1:15">
       <c r="A17" s="10">
         <v>15</v>
       </c>
-      <c r="B17" s="11">
-        <v>15</v>
-      </c>
-      <c r="C17" s="10">
-        <v>15</v>
-      </c>
-      <c r="D17" s="10">
-        <v>15</v>
-      </c>
-      <c r="E17" s="10">
-        <v>15</v>
-      </c>
-      <c r="F17" s="10">
-        <v>15</v>
-      </c>
-      <c r="G17" s="10">
-        <v>15</v>
-      </c>
-      <c r="H17" s="10">
-        <v>15</v>
-      </c>
-      <c r="I17" s="11">
-        <v>15</v>
-      </c>
-      <c r="J17" s="10">
-        <v>15</v>
-      </c>
-      <c r="K17" s="10">
-        <v>15</v>
-      </c>
-      <c r="L17" s="10">
-        <v>15</v>
-      </c>
-      <c r="M17" s="10">
-        <v>15</v>
-      </c>
-      <c r="N17" s="10">
-        <v>15</v>
-      </c>
-      <c r="O17" s="10">
-        <v>15</v>
-      </c>
+      <c r="B17" s="11"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="10"/>
+      <c r="K17" s="10"/>
+      <c r="L17" s="10"/>
+      <c r="M17" s="10"/>
+      <c r="N17" s="10"/>
+      <c r="O17" s="10"/>
     </row>
     <row r="18" ht="18" customHeight="1" spans="1:15">
-      <c r="A18" s="12">
+      <c r="A18" s="15">
         <v>16</v>
       </c>
-      <c r="B18" s="11">
-        <v>16</v>
-      </c>
-      <c r="C18" s="10">
-        <v>16</v>
-      </c>
-      <c r="D18" s="10">
-        <v>16</v>
-      </c>
-      <c r="E18" s="10">
-        <v>16</v>
-      </c>
-      <c r="F18" s="10">
-        <v>16</v>
-      </c>
-      <c r="G18" s="10">
-        <v>16</v>
-      </c>
-      <c r="H18" s="10">
-        <v>16</v>
-      </c>
-      <c r="I18" s="11">
-        <v>16</v>
-      </c>
-      <c r="J18" s="10">
-        <v>16</v>
-      </c>
-      <c r="K18" s="10">
-        <v>16</v>
-      </c>
-      <c r="L18" s="10">
-        <v>16</v>
-      </c>
-      <c r="M18" s="10">
-        <v>16</v>
-      </c>
-      <c r="N18" s="10">
-        <v>16</v>
-      </c>
-      <c r="O18" s="10">
-        <v>16</v>
-      </c>
+      <c r="B18" s="11"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="10"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="10"/>
+      <c r="M18" s="10"/>
+      <c r="N18" s="10"/>
+      <c r="O18" s="10"/>
     </row>
     <row r="19" ht="18" customHeight="1" spans="1:15">
       <c r="A19" s="10">
         <v>17</v>
       </c>
-      <c r="B19" s="11">
-        <v>17</v>
-      </c>
-      <c r="C19" s="10">
-        <v>17</v>
-      </c>
-      <c r="D19" s="10">
-        <v>17</v>
-      </c>
-      <c r="E19" s="10">
-        <v>17</v>
-      </c>
-      <c r="F19" s="10">
-        <v>17</v>
-      </c>
-      <c r="G19" s="10">
-        <v>17</v>
-      </c>
-      <c r="H19" s="10">
-        <v>17</v>
-      </c>
-      <c r="I19" s="11">
-        <v>17</v>
-      </c>
-      <c r="J19" s="10">
-        <v>17</v>
-      </c>
-      <c r="K19" s="10">
-        <v>17</v>
-      </c>
-      <c r="L19" s="10">
-        <v>17</v>
-      </c>
-      <c r="M19" s="10">
-        <v>17</v>
-      </c>
-      <c r="N19" s="10">
-        <v>17</v>
-      </c>
-      <c r="O19" s="10">
-        <v>17</v>
-      </c>
+      <c r="B19" s="11"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="10"/>
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+      <c r="M19" s="10"/>
+      <c r="N19" s="10"/>
+      <c r="O19" s="10"/>
     </row>
     <row r="20" ht="18" customHeight="1" spans="1:15">
-      <c r="A20" s="12">
+      <c r="A20" s="15">
         <v>18</v>
       </c>
-      <c r="B20" s="11">
-        <v>18</v>
-      </c>
-      <c r="C20" s="10">
-        <v>18</v>
-      </c>
-      <c r="D20" s="10">
-        <v>18</v>
-      </c>
-      <c r="E20" s="10">
-        <v>18</v>
-      </c>
-      <c r="F20" s="10">
-        <v>18</v>
-      </c>
-      <c r="G20" s="10">
-        <v>18</v>
-      </c>
-      <c r="H20" s="10">
-        <v>18</v>
-      </c>
-      <c r="I20" s="11">
-        <v>18</v>
-      </c>
-      <c r="J20" s="10">
-        <v>18</v>
-      </c>
-      <c r="K20" s="10">
-        <v>18</v>
-      </c>
-      <c r="L20" s="10">
-        <v>18</v>
-      </c>
-      <c r="M20" s="10">
-        <v>18</v>
-      </c>
-      <c r="N20" s="10">
-        <v>18</v>
-      </c>
-      <c r="O20" s="10">
-        <v>18</v>
-      </c>
+      <c r="B20" s="11"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="10"/>
+      <c r="K20" s="10"/>
+      <c r="L20" s="10"/>
+      <c r="M20" s="10"/>
+      <c r="N20" s="10"/>
+      <c r="O20" s="10"/>
     </row>
     <row r="21" ht="18" customHeight="1" spans="1:15">
       <c r="A21" s="10">
         <v>19</v>
       </c>
-      <c r="B21" s="11">
-        <v>19</v>
-      </c>
-      <c r="C21" s="10">
-        <v>19</v>
-      </c>
-      <c r="D21" s="10">
-        <v>19</v>
-      </c>
-      <c r="E21" s="10">
-        <v>19</v>
-      </c>
-      <c r="F21" s="10">
-        <v>19</v>
-      </c>
-      <c r="G21" s="10">
-        <v>19</v>
-      </c>
-      <c r="H21" s="10">
-        <v>19</v>
-      </c>
-      <c r="I21" s="11">
-        <v>19</v>
-      </c>
-      <c r="J21" s="10">
-        <v>19</v>
-      </c>
-      <c r="K21" s="10">
-        <v>19</v>
-      </c>
-      <c r="L21" s="10">
-        <v>19</v>
-      </c>
-      <c r="M21" s="10">
-        <v>19</v>
-      </c>
-      <c r="N21" s="10">
-        <v>19</v>
-      </c>
-      <c r="O21" s="10">
-        <v>19</v>
-      </c>
+      <c r="B21" s="11"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+      <c r="N21" s="10"/>
+      <c r="O21" s="10"/>
     </row>
     <row r="22" ht="18" customHeight="1" spans="1:15">
-      <c r="A22" s="12">
+      <c r="A22" s="15">
         <v>20</v>
       </c>
-      <c r="B22" s="11">
-        <v>20</v>
-      </c>
-      <c r="C22" s="10">
-        <v>20</v>
-      </c>
-      <c r="D22" s="10">
-        <v>20</v>
-      </c>
-      <c r="E22" s="10">
-        <v>20</v>
-      </c>
-      <c r="F22" s="10">
-        <v>20</v>
-      </c>
-      <c r="G22" s="10">
-        <v>20</v>
-      </c>
-      <c r="H22" s="10">
-        <v>20</v>
-      </c>
-      <c r="I22" s="11">
-        <v>20</v>
-      </c>
-      <c r="J22" s="10">
-        <v>20</v>
-      </c>
-      <c r="K22" s="10">
-        <v>20</v>
-      </c>
-      <c r="L22" s="10">
-        <v>20</v>
-      </c>
-      <c r="M22" s="10">
-        <v>20</v>
-      </c>
-      <c r="N22" s="10">
-        <v>20</v>
-      </c>
-      <c r="O22" s="10">
-        <v>20</v>
-      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="11"/>
+      <c r="J22" s="10"/>
+      <c r="K22" s="10"/>
+      <c r="L22" s="10"/>
+      <c r="M22" s="10"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
     </row>
     <row r="23" ht="18" customHeight="1" spans="1:15">
       <c r="A23" s="10">
         <v>21</v>
       </c>
-      <c r="B23" s="11">
-        <v>21</v>
-      </c>
-      <c r="C23" s="10">
-        <v>21</v>
-      </c>
-      <c r="D23" s="10">
-        <v>21</v>
-      </c>
-      <c r="E23" s="10">
-        <v>21</v>
-      </c>
-      <c r="F23" s="10">
-        <v>21</v>
-      </c>
-      <c r="G23" s="10">
-        <v>21</v>
-      </c>
-      <c r="H23" s="10">
-        <v>21</v>
-      </c>
-      <c r="I23" s="11">
-        <v>21</v>
-      </c>
-      <c r="J23" s="10">
-        <v>21</v>
-      </c>
-      <c r="K23" s="10">
-        <v>21</v>
-      </c>
-      <c r="L23" s="10">
-        <v>21</v>
-      </c>
-      <c r="M23" s="10">
-        <v>21</v>
-      </c>
-      <c r="N23" s="10">
-        <v>21</v>
-      </c>
-      <c r="O23" s="10">
-        <v>21</v>
-      </c>
+      <c r="B23" s="11"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="10"/>
+      <c r="K23" s="10"/>
+      <c r="L23" s="10"/>
+      <c r="M23" s="10"/>
+      <c r="N23" s="10"/>
+      <c r="O23" s="10"/>
     </row>
     <row r="24" ht="18" customHeight="1" spans="1:15">
-      <c r="A24" s="12">
+      <c r="A24" s="15">
         <v>22</v>
       </c>
-      <c r="B24" s="11">
-        <v>22</v>
-      </c>
-      <c r="C24" s="10">
-        <v>22</v>
-      </c>
-      <c r="D24" s="10">
-        <v>22</v>
-      </c>
-      <c r="E24" s="10">
-        <v>22</v>
-      </c>
-      <c r="F24" s="10">
-        <v>22</v>
-      </c>
-      <c r="G24" s="10">
-        <v>22</v>
-      </c>
-      <c r="H24" s="10">
-        <v>22</v>
-      </c>
-      <c r="I24" s="11">
-        <v>22</v>
-      </c>
-      <c r="J24" s="10">
-        <v>22</v>
-      </c>
-      <c r="K24" s="10">
-        <v>22</v>
-      </c>
-      <c r="L24" s="10">
-        <v>22</v>
-      </c>
-      <c r="M24" s="10">
-        <v>22</v>
-      </c>
-      <c r="N24" s="10">
-        <v>22</v>
-      </c>
-      <c r="O24" s="10">
-        <v>22</v>
-      </c>
+      <c r="B24" s="11"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="11"/>
+      <c r="J24" s="10"/>
+      <c r="K24" s="10"/>
+      <c r="L24" s="10"/>
+      <c r="M24" s="10"/>
+      <c r="N24" s="10"/>
+      <c r="O24" s="10"/>
     </row>
     <row r="25" ht="18" customHeight="1" spans="1:15">
       <c r="A25" s="10">
         <v>23</v>
       </c>
-      <c r="B25" s="11">
-        <v>23</v>
-      </c>
-      <c r="C25" s="10">
-        <v>23</v>
-      </c>
-      <c r="D25" s="10">
-        <v>23</v>
-      </c>
-      <c r="E25" s="10">
-        <v>23</v>
-      </c>
-      <c r="F25" s="10">
-        <v>23</v>
-      </c>
-      <c r="G25" s="10">
-        <v>23</v>
-      </c>
-      <c r="H25" s="10">
-        <v>23</v>
-      </c>
-      <c r="I25" s="11">
-        <v>23</v>
-      </c>
-      <c r="J25" s="10">
-        <v>23</v>
-      </c>
-      <c r="K25" s="10">
-        <v>23</v>
-      </c>
-      <c r="L25" s="10">
-        <v>23</v>
-      </c>
-      <c r="M25" s="10">
-        <v>23</v>
-      </c>
-      <c r="N25" s="10">
-        <v>23</v>
-      </c>
-      <c r="O25" s="10">
-        <v>23</v>
-      </c>
+      <c r="B25" s="11"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="11"/>
+      <c r="J25" s="10"/>
+      <c r="K25" s="10"/>
+      <c r="L25" s="10"/>
+      <c r="M25" s="10"/>
+      <c r="N25" s="10"/>
+      <c r="O25" s="10"/>
     </row>
     <row r="26" ht="18" customHeight="1" spans="1:15">
-      <c r="A26" s="12">
+      <c r="A26" s="15">
         <v>24</v>
       </c>
-      <c r="B26" s="11">
-        <v>24</v>
-      </c>
-      <c r="C26" s="10">
-        <v>24</v>
-      </c>
-      <c r="D26" s="10">
-        <v>24</v>
-      </c>
-      <c r="E26" s="10">
-        <v>24</v>
-      </c>
-      <c r="F26" s="10">
-        <v>24</v>
-      </c>
-      <c r="G26" s="10">
-        <v>24</v>
-      </c>
-      <c r="H26" s="10">
-        <v>24</v>
-      </c>
-      <c r="I26" s="11">
-        <v>24</v>
-      </c>
-      <c r="J26" s="10">
-        <v>24</v>
-      </c>
-      <c r="K26" s="10">
-        <v>24</v>
-      </c>
-      <c r="L26" s="10">
-        <v>24</v>
-      </c>
-      <c r="M26" s="10">
-        <v>24</v>
-      </c>
-      <c r="N26" s="10">
-        <v>24</v>
-      </c>
-      <c r="O26" s="10">
-        <v>24</v>
-      </c>
+      <c r="B26" s="11"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="11"/>
+      <c r="J26" s="10"/>
+      <c r="K26" s="10"/>
+      <c r="L26" s="10"/>
+      <c r="M26" s="10"/>
+      <c r="N26" s="10"/>
+      <c r="O26" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4770,80 +4200,80 @@
   <sheetData>
     <row r="1" ht="30" customHeight="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" ht="25" customHeight="1" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" ht="40" customHeight="1" spans="1:4">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" spans="1:4">
       <c r="A6" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" spans="1:4">
       <c r="A7" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="8"/>
     </row>
     <row r="8" ht="22" customHeight="1" spans="1:4">
       <c r="A8" s="5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="8"/>
     </row>
     <row r="9" ht="22" customHeight="1" spans="1:4">
       <c r="A9" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="8"/>
     </row>
     <row r="10" ht="22" customHeight="1" spans="1:4">
       <c r="A10" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="8"/>
     </row>
     <row r="12" ht="25" customHeight="1" spans="1:4">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" spans="1:4">
       <c r="A13" s="9" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" spans="1:4">
       <c r="A14" s="9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
